--- a/data/argentina/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/argentina/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,436 +425,432 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S17"/>
+  <dimension ref="A1:U16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_home_1</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_1</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_1</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_2</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_2</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_2</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_3</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_3</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_4</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_4</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_3</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_3</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_4</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_4</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_5</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_5</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>noM4eJv9</t>
+          <t>fotMKZ7K</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EqSQs1s2</t>
+          <t>xCPSwC5n</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>sotelo david</t>
+          <t>alvarez fabio</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>hbEDsmqs</t>
+          <t>0Cik0ca1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>urzua javier</t>
+          <t>carrera ramiro</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>dpvMFJWA</t>
+          <t>bTfes3EB</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>mendez mauro</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+          <t>diaz leandro</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>fHXm67sB</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>loaiza raul</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>vkxiXNZh</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>sanabria mateo</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>GOvBwyO7</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>soler julio</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>nkx6zI2q</t>
+          <t>YHCv8dOE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>C61C6jIC</t>
+          <t>2ZHRgVea</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>cejas juan</t>
+          <t>gomez matias</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2exniD8K</t>
+          <t>40njcyiS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>sanchez luciano</t>
+          <t>palacios sebastian</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>jFOodCcg</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>pozzo tomas</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>QZAc3PWF</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>salvareschi braian</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>8rZQ1Vsm</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>puig maximiliano</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>pdWqnF1e</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>fZ8t9oiS</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>fernandez damian</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>SO4kc7ts</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>alanis gabriel</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>StlNL0Sr</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>barbona david</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>faBFjCzE</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>gomez valentin</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>hjIfdnOs</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>gordillo yeison</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>O6l8vedq</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>mammana emanuel</t>
-        </is>
-      </c>
+          <t>llkWcC07</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>tpCGHIpe</t>
+          <t>xE00PZW2</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>bogarin rodrigo</t>
+          <t>passerini lucas</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>U3udhQNE</t>
+          <t>Q3tsV415</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>togni gaston</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>63NhFg3j</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>tripichio nicolas</t>
-        </is>
-      </c>
+          <t>sanchez ulises</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>vq1qlyXr</t>
+          <t>hMeNaYVf</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>v7raiufc</t>
+          <t>8hwz7Jmi</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>matias galarza</t>
+          <t>chavez lautaro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>vVQ6dAPA</t>
+          <t>jNBjnvc1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>bochi roberto</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+          <t>colman cristian</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>hr0J2uKo</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>esquivel juan</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2ZHRgVea</t>
+          <t>bu69MoY1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>gomez matias</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>mammini ivo</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>EqpFUuyl</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>mamut leandro</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>hQEvrfQF</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>garcia basso agustin</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>U9B9fwfF</t>
+          <t>trGn6zgR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>40Q5CqWD</t>
+          <t>nen2ZiHf</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>gimenez matias</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>hfaKzF13</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>hausch agustin</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>zVe6huUq</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>hernandez gaston</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>l0CEyg0b</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>gonzalez lucas</t>
-        </is>
-      </c>
+          <t>ambrogio lucas</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
+          <t>hfaKzF13</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>hausch agustin</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>zVe6huUq</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>hernandez gaston</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
           <t>QoRw6kJd</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>insaurralde manuel</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>KvUIXFn2</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>hQEvrfQF</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>garcia basso agustin</t>
-        </is>
-      </c>
+          <t>badJ0EGl</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>EqSQs1s2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>sotelo david</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -863,88 +859,108 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>YF1eCyBq</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>bravo agustin antonio</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>tdP9bc0T</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>hernandez abel</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>8zv0bGeF</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>komar juan</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>tWCCM4V2</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>malcorra victor</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bPuAZyIk</t>
+          <t>2iHr7GwL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GIIVeUW1</t>
+          <t>fapdUrRo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mauri jose</t>
+          <t>blondel lucas</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>ttsQAp6D</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>molina avalos agustin</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>KC5nBJcI</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>paradela federico</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>MTnzNzCB</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>castro federico</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>jJu38XHd</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>gomez luciano</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>tlVEYeXe</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>6RPCVUS3</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>vera federico</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>t6VfIMMj</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>martinez gonzalo</t>
-        </is>
-      </c>
+          <t>WCfRbho1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -953,37 +969,55 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>t6VfIMMj</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>martinez gonzalo</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>xdJdDfIi</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>sant anna agustin</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>xzFHhHOR</t>
+          <t>vJVmoZG1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>fapdUrRo</t>
+          <t>StlNL0Sr</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>blondel lucas</t>
+          <t>barbona david</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8rZQ1Vsm</t>
+          <t>U3udhQNE</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>puig maximiliano</t>
+          <t>togni gaston</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -994,78 +1028,138 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>nHhatngb</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>gomez jose amado</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2qY241h8</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>montoya lautaro</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>rDFDgc9L</t>
+          <t>fRDz9x98</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nen2ZiHf</t>
+          <t>vyXoMETf</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ambrogio lucas</t>
+          <t>goicochea juan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MTnzNzCB</t>
+          <t>Gl1otypH</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>castro federico</t>
+          <t>hachen gabriel</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>jJu38XHd</t>
+          <t>vZfTMp8j</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>gomez luciano</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+          <t>lozano raul</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>bTIMYsm5</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>picco leonel</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Eg8FK4h5</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>rius ciro</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hOz1lSPe</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>saborido juan</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>vVQ6dAPA</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>bochi roberto</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>U9kvubfS</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
+          <t>hMZipgW7</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>hjIfdnOs</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>gordillo yeison</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8UAUMZKi</t>
+          <t>vXmpTaDK</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>protti ijiel</t>
+          <t>lagos augustin</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -1076,23 +1170,73 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>ARE7Jw9d</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>cabrera alejandro</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>rRiQUBkp</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>maldonado alexis</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>t2Y9XjeB</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>palavecino lucas</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2Je6f1HR</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>perez mateo</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>jJjztvuM</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+          <t>nPhF1f1r</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>40Q5CqWD</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>gimenez matias</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>fZNeCQQl</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>luna alex</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
@@ -1101,17 +1245,35 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>hbEDsmqs</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>urzua javier</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>dpvMFJWA</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>mendez mauro</t>
+        </is>
+      </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>8fN0daP2</t>
+          <t>trxILFhE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -1132,11 +1294,13 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>65Xumenk</t>
+          <t>Y9EiyTMr</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -1157,11 +1321,13 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>SvlzcWFD</t>
+          <t>fgvPVMI8</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -1182,31 +1348,8 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>ngdGLTFj</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
